--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.67</v>
+        <v>-2.56</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Alcista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>No Convencente / Correctivo</t>
+          <t>Sí (Posible Onda de Impulso)</t>
         </is>
       </c>
     </row>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4477.2001953125</v>
+        <v>4469.89990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0002009562814866417</v>
+        <v>0.0280358561048184</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05544559059700616</v>
+        <v>0.02478336982363971</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>66.81999969482422</v>
+        <v>67.22499847412109</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.002612180678905007</v>
+        <v>0.04034483287896373</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08758281532845325</v>
+        <v>0.03254685551446568</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.56</v>
+        <v>-2.83</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alcista</t>
+          <t>Bajista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sí (Posible Onda de Impulso)</t>
+          <t>No Convencente / Correctivo</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>108120.1866378784</v>
+        <v>107209.7581695557</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+48.9%</t>
+          <t>+49.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-62201.15684509277</v>
+        <v>-61793.33684692383</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+36.1%</t>
+          <t>+36.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-45919.02979278565</v>
+        <v>-45416.42132263183</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51.34</v>
+        <v>51</v>
       </c>
       <c r="C2" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="D2" t="n">
-        <v>50.36</v>
+        <v>50.47</v>
       </c>
       <c r="E2" t="n">
-        <v>58.11</v>
+        <v>57.64</v>
       </c>
       <c r="F2" t="n">
-        <v>543.09</v>
+        <v>293.43</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.68</v>
+        <v>20.46</v>
       </c>
       <c r="C3" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="D3" t="n">
-        <v>18.75</v>
+        <v>18.86</v>
       </c>
       <c r="E3" t="n">
-        <v>24.21</v>
+        <v>23.86</v>
       </c>
       <c r="F3" t="n">
-        <v>4881.1</v>
+        <v>4056.33</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>266.18</v>
+        <v>264.31</v>
       </c>
       <c r="C5" t="n">
-        <v>9.01</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>251.46</v>
+        <v>251.41</v>
       </c>
       <c r="E5" t="n">
-        <v>293.21</v>
+        <v>291.39</v>
       </c>
       <c r="F5" t="n">
-        <v>2576.87</v>
+        <v>2257.12</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>51.34000015258789</v>
+        <v>51</v>
       </c>
       <c r="F5" t="n">
-        <v>28339.68008422852</v>
+        <v>28152</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>28339.68008422852</v>
+        <v>28152</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>266.1799926757812</v>
+        <v>264.3099975585938</v>
       </c>
       <c r="F6" t="n">
-        <v>46581.49871826172</v>
+        <v>46254.24957275391</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>46581.49871826172</v>
+        <v>46254.24957275391</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20.68000030517578</v>
+        <v>20.45999908447266</v>
       </c>
       <c r="F7" t="n">
-        <v>52279.04077148438</v>
+        <v>51722.87768554688</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>52279.04077148438</v>
+        <v>51722.87768554688</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4469.89990234375</v>
+        <v>4400.10009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0280358561048184</v>
+        <v>0.007741175475963313</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02478336982363971</v>
+        <v>0.003901459652349892</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>67.22499847412109</v>
+        <v>66.31500244140625</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04034483287896373</v>
+        <v>0.02459717378924631</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03254685551446568</v>
+        <v>0.02386952579227608</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.83</v>
+        <v>-2.78</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Alcista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>No Convencente / Correctivo</t>
+          <t>Sí (Posible Onda de Impulso)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>107209.7581695557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+49.0%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-61793.33684692383</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+36.0%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-45416.42132263183</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -717,20 +717,12 @@
           <t>PAAS</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>51</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="D2" t="n">
-        <v>50.47</v>
-      </c>
-      <c r="E2" t="n">
-        <v>57.64</v>
-      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>293.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -739,20 +731,12 @@
           <t>HL</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>20.46</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="D3" t="n">
-        <v>18.86</v>
-      </c>
-      <c r="E3" t="n">
-        <v>23.86</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>4056.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -775,20 +759,12 @@
           <t>FNV</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>264.31</v>
-      </c>
-      <c r="C5" t="n">
-        <v>9.029999999999999</v>
-      </c>
-      <c r="D5" t="n">
-        <v>251.41</v>
-      </c>
-      <c r="E5" t="n">
-        <v>291.39</v>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>2257.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -980,20 +956,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>51</v>
-      </c>
-      <c r="F5" t="n">
-        <v>28152</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Layer 2</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>28152</v>
-      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1012,20 +982,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>264.3099975585938</v>
-      </c>
-      <c r="F6" t="n">
-        <v>46254.24957275391</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Layer 2</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>46254.24957275391</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1044,20 +1008,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>20.45999908447266</v>
-      </c>
-      <c r="F7" t="n">
-        <v>51722.87768554688</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Layer 3</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>51722.87768554688</v>
-      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1108,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4400.10009765625</v>
+        <v>4437.7998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007741175475963313</v>
+        <v>-0.01199999739102131</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003901459652349892</v>
+        <v>0.006554900992056245</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>66.31500244140625</v>
+        <v>67.81999969482422</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02459717378924631</v>
+        <v>0.01264688945505865</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02386952579227608</v>
+        <v>0.03455113079252947</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.78</v>
+        <v>-2.52</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alcista</t>
+          <t>Bajista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sí (Posible Onda de Impulso)</t>
+          <t>No Convencente / Correctivo</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>105557.1332443237</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>+49.2%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-61155.81521911622</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>+35.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-44401.31802520753</v>
       </c>
     </row>
   </sheetData>
@@ -717,12 +717,20 @@
           <t>PAAS</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>50.65</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="D2" t="n">
+        <v>48.58</v>
+      </c>
+      <c r="E2" t="n">
+        <v>56.86</v>
+      </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1142.85</v>
       </c>
     </row>
     <row r="3">
@@ -731,12 +739,20 @@
           <t>HL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="D3" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="E3" t="n">
+        <v>23.05</v>
+      </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2160.73</v>
       </c>
     </row>
     <row r="4">
@@ -759,12 +775,20 @@
           <t>FNV</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>260.66</v>
+      </c>
+      <c r="C5" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>253.72</v>
+      </c>
+      <c r="E5" t="n">
+        <v>284.97</v>
+      </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1214.48</v>
       </c>
     </row>
     <row r="6">
@@ -956,14 +980,20 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>50.65000152587891</v>
+      </c>
+      <c r="F5" t="n">
+        <v>27958.80084228516</v>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Layer 2</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>27958.80084228516</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -982,14 +1012,20 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>260.6600036621094</v>
+      </c>
+      <c r="F6" t="n">
+        <v>45615.50064086914</v>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Layer 2</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>45615.50064086914</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1008,14 +1044,20 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>20.02000045776367</v>
+      </c>
+      <c r="F7" t="n">
+        <v>50610.56115722656</v>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Layer 3</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>50610.56115722656</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1066,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4437.7998046875</v>
+        <v>4356.7998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.01199999739102131</v>
+        <v>-0.01647930001774645</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006554900992056245</v>
+        <v>-0.001558413423907168</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>67.81999969482422</v>
+        <v>64.04000091552734</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01264688945505865</v>
+        <v>-0.03038739448893557</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03455113079252947</v>
+        <v>-0.01284047552908762</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Alcista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105557.1332443237</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+49.2%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-61155.81521911622</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+35.8%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-44401.31802520753</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -717,20 +717,12 @@
           <t>PAAS</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>50.65</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="D2" t="n">
-        <v>48.58</v>
-      </c>
-      <c r="E2" t="n">
-        <v>56.86</v>
-      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>1142.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -739,20 +731,12 @@
           <t>HL</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>20.02</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="D3" t="n">
-        <v>19.17</v>
-      </c>
-      <c r="E3" t="n">
-        <v>23.05</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>2160.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -775,20 +759,12 @@
           <t>FNV</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>260.66</v>
-      </c>
-      <c r="C5" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>253.72</v>
-      </c>
-      <c r="E5" t="n">
-        <v>284.97</v>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>1214.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -980,20 +956,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>50.65000152587891</v>
-      </c>
-      <c r="F5" t="n">
-        <v>27958.80084228516</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Layer 2</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>27958.80084228516</v>
-      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1012,20 +982,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>260.6600036621094</v>
-      </c>
-      <c r="F6" t="n">
-        <v>45615.50064086914</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Layer 2</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>45615.50064086914</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1044,20 +1008,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>20.02000045776367</v>
-      </c>
-      <c r="F7" t="n">
-        <v>50610.56115722656</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Layer 3</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>50610.56115722656</v>
-      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1108,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4356.7998046875</v>
+        <v>4390</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.01647930001774645</v>
+        <v>-0.008984560576616785</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.001558413423907168</v>
+        <v>0.006050027901944866</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64.04000091552734</v>
+        <v>65.01999664306641</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.03038739448893557</v>
+        <v>-0.01554954006694309</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.01284047552908762</v>
+        <v>0.00226589709037972</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4390</v>
+        <v>4327.60009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.008984560576616785</v>
+        <v>-0.02307095388895564</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006050027901944866</v>
+        <v>-0.01205364940750031</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65.01999664306641</v>
+        <v>63.53499984741211</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.01554954006694309</v>
+        <v>-0.03803348122286565</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00226589709037972</v>
+        <v>-0.02235796051869265</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.52</v>
+        <v>-2.32</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alcista</t>
+          <t>Bajista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4327.60009765625</v>
+        <v>4323.7998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02307095388895564</v>
+        <v>-0.03069033663568355</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.01205364940750031</v>
+        <v>-0.0218975457698769</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63.53499984741211</v>
+        <v>64.19499969482422</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.03803348122286565</v>
+        <v>-0.05515000403130987</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02235796051869265</v>
+        <v>0.003972377585872655</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.32</v>
+        <v>-2.21</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4323.7998046875</v>
+        <v>4310.10009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.03069033663568355</v>
+        <v>-0.02205425347462653</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0218975457698769</v>
+        <v>-0.0517456971240251</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64.19499969482422</v>
+        <v>63.66500091552734</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.05515000403130987</v>
+        <v>-0.009629078766346111</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003972377585872655</v>
+        <v>-0.03147534316548029</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.21</v>
+        <v>-2.13</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4310.10009765625</v>
+        <v>4383.89990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02205425347462653</v>
+        <v>-0.005309351163009679</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0517456971240251</v>
+        <v>-0.03550918735378039</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63.66500091552734</v>
+        <v>65.91500091552734</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.009629078766346111</v>
+        <v>0.02537185645287021</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.03147534316548029</v>
+        <v>0.002753518006909816</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.13</v>
+        <v>-2.23</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Alcista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4383.89990234375</v>
+        <v>4415.89990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.005309351163009679</v>
+        <v>0.001587697646816322</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.03550918735378039</v>
+        <v>-0.03401583832564625</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65.91500091552734</v>
+        <v>66.78500366210938</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02537185645287021</v>
+        <v>0.03456025618994518</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002753518006909816</v>
+        <v>-0.01824298498570709</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.23</v>
+        <v>-1.93</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>COMPRAR SPREAD (Largo GLD / Corto GDX)</t>
+          <t>MANTENER</t>
         </is>
       </c>
     </row>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4415.89990234375</v>
+        <v>4396.89990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001587697646816322</v>
+        <v>0.01479415171384146</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.03401583832564625</v>
+        <v>-0.06405123991097061</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>66.78500366210938</v>
+        <v>66.98500061035156</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03456025618994518</v>
+        <v>0.05928585846191869</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.01824298498570709</v>
+        <v>-0.02270173688078303</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.93</v>
+        <v>-1.92</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alcista</t>
+          <t>Bajista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4396.89990234375</v>
+        <v>4406.2998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01479415171384146</v>
+        <v>0.004284855769230766</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.06405123991097061</v>
+        <v>-0.06139103106028332</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>66.98500061035156</v>
+        <v>68.02500152587891</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05928585846191869</v>
+        <v>0.05812903488423293</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02270173688078303</v>
+        <v>-0.008902034601497633</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.92</v>
+        <v>-2.36</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MANTENER</t>
+          <t>COMPRAR SPREAD (Largo GLD / Corto GDX)</t>
         </is>
       </c>
     </row>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4406.2998046875</v>
+        <v>4325.39990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004284855769230766</v>
+        <v>-0.01688758089651443</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.06139103106028332</v>
+        <v>-0.07046610278870069</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>68.02500152587891</v>
+        <v>64.68499755859375</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05812903488423293</v>
+        <v>-0.01199028024244386</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.008902034601497633</v>
+        <v>-0.0486100957349338</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.36</v>
+        <v>-2.09</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4325.39990234375</v>
+        <v>4302.5</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.01688758089651443</v>
+        <v>-0.02766162061178334</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.07046610278870069</v>
+        <v>-0.07750857632933106</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64.68499755859375</v>
+        <v>64.12999725341797</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.01199028024244386</v>
+        <v>-0.03645054557576277</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0486100957349338</v>
+        <v>-0.0763226250681579</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.09</v>
+        <v>-1.96</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>COMPRAR SPREAD (Largo GLD / Corto GDX)</t>
+          <t>MANTENER</t>
         </is>
       </c>
     </row>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4302.5</v>
+        <v>4320.5</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02766162061178334</v>
+        <v>-0.0235937319821522</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.07750857632933106</v>
+        <v>-0.07364922813036023</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64.12999725341797</v>
+        <v>64.70999908447266</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.03645054557576277</v>
+        <v>-0.02773605201872431</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0763226250681579</v>
+        <v>-0.06796874089992333</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.96</v>
+        <v>-2.07</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MANTENER</t>
+          <t>COMPRAR SPREAD (Largo GLD / Corto GDX)</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LIGERAMENTE ALCISTA (Parcial)</t>
+          <t>HOLD / CASH (Sin Tendencia)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>94590.60984344482</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>+51.4%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-57153.48278503418</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>+33.6%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-37437.12705841065</v>
       </c>
     </row>
   </sheetData>
@@ -717,12 +717,20 @@
           <t>PAAS</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>45.77</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.63</v>
+      </c>
+      <c r="E2" t="n">
+        <v>52.19</v>
+      </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1181.28</v>
       </c>
     </row>
     <row r="3">
@@ -731,12 +739,20 @@
           <t>HL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20.02</v>
+      </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2535.22</v>
       </c>
     </row>
     <row r="4">
@@ -759,12 +775,20 @@
           <t>FNV</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>245.81</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="D5" t="n">
+        <v>237.89</v>
+      </c>
+      <c r="E5" t="n">
+        <v>269.58</v>
+      </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1386.59</v>
       </c>
     </row>
     <row r="6">
@@ -956,14 +980,20 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>45.77000045776367</v>
+      </c>
+      <c r="F5" t="n">
+        <v>25265.04025268555</v>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Layer 2</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>25265.04025268555</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -982,14 +1012,20 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>245.8099975585938</v>
+      </c>
+      <c r="F6" t="n">
+        <v>43016.74957275391</v>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Layer 2</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>43016.74957275391</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1008,14 +1044,20 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>17.01000022888184</v>
+      </c>
+      <c r="F7" t="n">
+        <v>43001.28057861328</v>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Layer 3</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>43001.28057861328</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1066,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4320.5</v>
+        <v>4161.5</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0235937319821522</v>
+        <v>-0.04910426540971768</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.07364922813036023</v>
+        <v>-0.07140466361709252</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64.70999908447266</v>
+        <v>61.05500030517578</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.02773605201872431</v>
+        <v>-0.07397013529180541</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.06796874089992333</v>
+        <v>-0.07801151166299281</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.07</v>
+        <v>-2.05</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>94590.60984344482</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.4%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-57153.48278503418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.6%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-37437.12705841065</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -717,20 +717,12 @@
           <t>PAAS</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>45.77</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="D2" t="n">
-        <v>43.63</v>
-      </c>
-      <c r="E2" t="n">
-        <v>52.19</v>
-      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>1181.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -739,20 +731,12 @@
           <t>HL</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>17.01</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>16.01</v>
-      </c>
-      <c r="E3" t="n">
-        <v>20.02</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>2535.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -775,20 +759,12 @@
           <t>FNV</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>245.81</v>
-      </c>
-      <c r="C5" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="D5" t="n">
-        <v>237.89</v>
-      </c>
-      <c r="E5" t="n">
-        <v>269.58</v>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>1386.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -980,20 +956,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>45.77000045776367</v>
-      </c>
-      <c r="F5" t="n">
-        <v>25265.04025268555</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Layer 2</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>25265.04025268555</v>
-      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1012,20 +982,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>245.8099975585938</v>
-      </c>
-      <c r="F6" t="n">
-        <v>43016.74957275391</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Layer 2</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>43016.74957275391</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1044,20 +1008,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>17.01000022888184</v>
-      </c>
-      <c r="F7" t="n">
-        <v>43001.28057861328</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Layer 3</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>43001.28057861328</v>
-      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1108,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4161.5</v>
+        <v>4212.2001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.04910426540971768</v>
+        <v>-0.02459237435921846</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.07140466361709252</v>
+        <v>-0.04189785076945618</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61.05500030517578</v>
+        <v>61.73500061035156</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.07397013529180541</v>
+        <v>-0.04111402283627841</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.07801151166299281</v>
+        <v>-0.04461598586003368</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.05</v>
+        <v>-1.9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>COMPRAR SPREAD (Largo GLD / Corto GDX)</t>
+          <t>MANTENER</t>
         </is>
       </c>
     </row>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4212.2001953125</v>
+        <v>4178.10009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02459237435921846</v>
+        <v>-0.02789667341641466</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04189785076945618</v>
+        <v>-0.05357223639023612</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61.73500061035156</v>
+        <v>60.56499862670898</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.04111402283627841</v>
+        <v>-0.04557420099174792</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.04461598586003368</v>
+        <v>-0.06424301984599756</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.9</v>
+        <v>-1.8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4178.10009765625</v>
+        <v>4173.2001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02789667341641466</v>
+        <v>-0.03424974389303825</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.05357223639023612</v>
+        <v>-0.08077264145007668</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60.56499862670898</v>
+        <v>60.68999862670898</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.04557420099174792</v>
+        <v>-0.05533510729069402</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.06424301984599756</v>
+        <v>-0.09381393973879859</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.8</v>
+        <v>-1.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4173.2001953125</v>
+        <v>4172.10009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.03424974389303825</v>
+        <v>-0.03450432539968618</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.08077264145007668</v>
+        <v>-0.08101495905176703</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60.68999862670898</v>
+        <v>60.70999908447266</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.05533510729069402</v>
+        <v>-0.05502379190570494</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.09381393973879859</v>
+        <v>-0.09351530509661055</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.5</v>
+        <v>-1.79</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>93631.25716705322</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>+51.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-56137.6975982666</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>+34.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-37493.55956878662</v>
       </c>
     </row>
   </sheetData>
@@ -717,12 +717,20 @@
           <t>PAAS</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>45.32</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.53</v>
+      </c>
+      <c r="E2" t="n">
+        <v>50.69</v>
+      </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>988.47</v>
       </c>
     </row>
     <row r="3">
@@ -731,12 +739,20 @@
           <t>HL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D3" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="E3" t="n">
+        <v>19.58</v>
+      </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2165.05</v>
       </c>
     </row>
     <row r="4">
@@ -759,12 +775,20 @@
           <t>FNV</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>240.78</v>
+      </c>
+      <c r="C5" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="D5" t="n">
+        <v>230.85</v>
+      </c>
+      <c r="E5" t="n">
+        <v>270.57</v>
+      </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1737.5</v>
       </c>
     </row>
     <row r="6">
@@ -956,14 +980,20 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>45.31999969482422</v>
+      </c>
+      <c r="F5" t="n">
+        <v>25016.63983154297</v>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Layer 2</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>25016.63983154297</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -982,14 +1012,20 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>240.7799987792969</v>
+      </c>
+      <c r="F6" t="n">
+        <v>42136.49978637695</v>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Layer 2</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>42136.49978637695</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1008,14 +1044,20 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>17.01000022888184</v>
+      </c>
+      <c r="F7" t="n">
+        <v>43001.28057861328</v>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Layer 3</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>43001.28057861328</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1066,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4172.10009765625</v>
+        <v>4156.7001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.03450432539968618</v>
+        <v>-0.005502787024245004</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.08101495905176703</v>
+        <v>-0.07146046002885886</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60.70999908447266</v>
+        <v>60.98500061035156</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.05502379190570494</v>
+        <v>0.005225182082819302</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.09351530509661055</v>
+        <v>-0.07664234082545829</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.79</v>
+        <v>-1.73</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>93631.25716705322</v>
+        <v>94582.16832504272</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.0%</t>
+          <t>+51.2%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-56137.6975982666</v>
+        <v>-56917.02432098388</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+34.0%</t>
+          <t>+33.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-37493.55956878662</v>
+        <v>-37665.14400405883</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45.32</v>
+        <v>45.92</v>
       </c>
       <c r="C2" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="D2" t="n">
-        <v>43.53</v>
+        <v>44.21</v>
       </c>
       <c r="E2" t="n">
-        <v>50.69</v>
+        <v>51.04</v>
       </c>
       <c r="F2" t="n">
-        <v>988.47</v>
+        <v>942.34</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.01</v>
+        <v>17.1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="D3" t="n">
-        <v>16.15</v>
+        <v>16.31</v>
       </c>
       <c r="E3" t="n">
-        <v>19.58</v>
+        <v>19.46</v>
       </c>
       <c r="F3" t="n">
-        <v>2165.05</v>
+        <v>1991.7</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>240.78</v>
+        <v>243.98</v>
       </c>
       <c r="C5" t="n">
-        <v>9.93</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>230.85</v>
+        <v>234.43</v>
       </c>
       <c r="E5" t="n">
-        <v>270.57</v>
+        <v>272.64</v>
       </c>
       <c r="F5" t="n">
-        <v>1737.5</v>
+        <v>1671.88</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>45.31999969482422</v>
+        <v>45.91999816894531</v>
       </c>
       <c r="F5" t="n">
-        <v>25016.63983154297</v>
+        <v>25347.83898925781</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>25016.63983154297</v>
+        <v>25347.83898925781</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>240.7799987792969</v>
+        <v>243.9799957275391</v>
       </c>
       <c r="F6" t="n">
-        <v>42136.49978637695</v>
+        <v>42696.49925231934</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>42136.49978637695</v>
+        <v>42696.49925231934</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.01000022888184</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="F7" t="n">
-        <v>43001.28057861328</v>
+        <v>43228.80096435547</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>43001.28057861328</v>
+        <v>43228.80096435547</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4156.7001953125</v>
+        <v>4180.2998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.005502787024245004</v>
+        <v>-0.001528743479689787</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.07146046002885886</v>
+        <v>-0.05827893564147335</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60.98500061035156</v>
+        <v>61.53499984741211</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005225182082819302</v>
+        <v>0.02391095019591449</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.07664234082545829</v>
+        <v>-0.07182824914151043</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.73</v>
+        <v>-1.66</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>94582.16832504272</v>
+        <v>91415.47406463623</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.2%</t>
+          <t>+51.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-56917.02432098388</v>
+        <v>-55358.93643493652</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.8%</t>
+          <t>+33.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-37665.14400405883</v>
+        <v>-36056.53762969971</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45.92</v>
+        <v>44.35</v>
       </c>
       <c r="C2" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="D2" t="n">
-        <v>44.21</v>
+        <v>42.68</v>
       </c>
       <c r="E2" t="n">
-        <v>51.04</v>
+        <v>49.37</v>
       </c>
       <c r="F2" t="n">
-        <v>942.34</v>
+        <v>923.8099999999999</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.1</v>
+        <v>16.39</v>
       </c>
       <c r="C3" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="D3" t="n">
-        <v>16.31</v>
+        <v>15.62</v>
       </c>
       <c r="E3" t="n">
-        <v>19.46</v>
+        <v>18.7</v>
       </c>
       <c r="F3" t="n">
-        <v>1991.7</v>
+        <v>1950.17</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>243.98</v>
+        <v>237.9</v>
       </c>
       <c r="C5" t="n">
-        <v>9.550000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="D5" t="n">
-        <v>234.43</v>
+        <v>228.41</v>
       </c>
       <c r="E5" t="n">
-        <v>272.64</v>
+        <v>266.37</v>
       </c>
       <c r="F5" t="n">
-        <v>1671.88</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>45.91999816894531</v>
+        <v>44.34999847412109</v>
       </c>
       <c r="F5" t="n">
-        <v>25347.83898925781</v>
+        <v>24481.19915771484</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>25347.83898925781</v>
+        <v>24481.19915771484</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>243.9799957275391</v>
+        <v>237.8999938964844</v>
       </c>
       <c r="F6" t="n">
-        <v>42696.49925231934</v>
+        <v>41632.49893188477</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>42696.49925231934</v>
+        <v>41632.49893188477</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.10000038146973</v>
+        <v>16.38999938964844</v>
       </c>
       <c r="F7" t="n">
-        <v>43228.80096435547</v>
+        <v>41433.91845703125</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>43228.80096435547</v>
+        <v>41433.91845703125</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4180.2998046875</v>
+        <v>4152.2998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.001528743479689787</v>
+        <v>-0.01189824675151141</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.05827893564147335</v>
+        <v>-0.0691372154867258</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61.53499984741211</v>
+        <v>60.52000045776367</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02391095019591449</v>
+        <v>-0.003375842264447093</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.07182824914151043</v>
+        <v>-0.1092402451844936</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.66</v>
+        <v>-1.68</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>91415.47406463623</v>
+        <v>92983.25066070557</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.5%</t>
+          <t>+51.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-55358.93643493652</v>
+        <v>-56159.41479797363</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.5%</t>
+          <t>+33.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-36056.53762969971</v>
+        <v>-36823.83586273194</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44.35</v>
+        <v>45.31</v>
       </c>
       <c r="C2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="D2" t="n">
-        <v>42.68</v>
+        <v>43.63</v>
       </c>
       <c r="E2" t="n">
-        <v>49.37</v>
+        <v>50.34</v>
       </c>
       <c r="F2" t="n">
-        <v>923.8099999999999</v>
+        <v>926.1799999999999</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.39</v>
+        <v>16.73</v>
       </c>
       <c r="C3" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="D3" t="n">
-        <v>15.62</v>
+        <v>15.97</v>
       </c>
       <c r="E3" t="n">
-        <v>18.7</v>
+        <v>19.01</v>
       </c>
       <c r="F3" t="n">
-        <v>1950.17</v>
+        <v>1924.89</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>237.9</v>
+        <v>240.5</v>
       </c>
       <c r="C5" t="n">
-        <v>9.49</v>
+        <v>9.48</v>
       </c>
       <c r="D5" t="n">
-        <v>228.41</v>
+        <v>231.02</v>
       </c>
       <c r="E5" t="n">
-        <v>266.37</v>
+        <v>268.95</v>
       </c>
       <c r="F5" t="n">
-        <v>1661</v>
+        <v>1659.75</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.34999847412109</v>
+        <v>45.31000137329102</v>
       </c>
       <c r="F5" t="n">
-        <v>24481.19915771484</v>
+        <v>25011.12075805664</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24481.19915771484</v>
+        <v>25011.12075805664</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>237.8999938964844</v>
+        <v>240.5</v>
       </c>
       <c r="F6" t="n">
-        <v>41632.49893188477</v>
+        <v>42087.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>41632.49893188477</v>
+        <v>42087.5</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.38999938964844</v>
+        <v>16.72999954223633</v>
       </c>
       <c r="F7" t="n">
-        <v>41433.91845703125</v>
+        <v>42293.43884277344</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>41433.91845703125</v>
+        <v>42293.43884277344</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4152.2998046875</v>
+        <v>4194.2001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.01189824675151141</v>
+        <v>0.007664126113422709</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0691372154867258</v>
+        <v>-0.04835151199570142</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60.52000045776367</v>
+        <v>60.27500152587891</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.003375842264447093</v>
+        <v>0.004968576784097678</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1092402451844936</v>
+        <v>-0.06236381166868743</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.68</v>
+        <v>-1.73</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>92983.25066070557</v>
+        <v>94811.33796691895</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-56159.41479797363</v>
+        <v>-57235.51626586914</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-36823.83586273194</v>
+        <v>-37575.8217010498</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45.31</v>
+        <v>46.27</v>
       </c>
       <c r="C2" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="D2" t="n">
-        <v>43.63</v>
+        <v>44.62</v>
       </c>
       <c r="E2" t="n">
-        <v>50.34</v>
+        <v>51.21</v>
       </c>
       <c r="F2" t="n">
-        <v>926.1799999999999</v>
+        <v>909.62</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.73</v>
+        <v>17.07</v>
       </c>
       <c r="C3" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="D3" t="n">
-        <v>15.97</v>
+        <v>16.35</v>
       </c>
       <c r="E3" t="n">
-        <v>19.01</v>
+        <v>19.24</v>
       </c>
       <c r="F3" t="n">
-        <v>1924.89</v>
+        <v>1829.19</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>240.5</v>
+        <v>244.85</v>
       </c>
       <c r="C5" t="n">
-        <v>9.48</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>231.02</v>
+        <v>235.21</v>
       </c>
       <c r="E5" t="n">
-        <v>268.95</v>
+        <v>273.78</v>
       </c>
       <c r="F5" t="n">
-        <v>1659.75</v>
+        <v>1687.75</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>45.31000137329102</v>
+        <v>46.27000045776367</v>
       </c>
       <c r="F5" t="n">
-        <v>25011.12075805664</v>
+        <v>25541.04025268555</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>25011.12075805664</v>
+        <v>25541.04025268555</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>240.5</v>
+        <v>244.8500061035156</v>
       </c>
       <c r="F6" t="n">
-        <v>42087.5</v>
+        <v>42848.75106811523</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>42087.5</v>
+        <v>42848.75106811523</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.72999954223633</v>
+        <v>17.06999969482422</v>
       </c>
       <c r="F7" t="n">
-        <v>42293.43884277344</v>
+        <v>43152.95922851562</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>42293.43884277344</v>
+        <v>43152.95922851562</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4194.2001953125</v>
+        <v>4220.2998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007664126113422709</v>
+        <v>0.01393460411830061</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04835151199570142</v>
+        <v>-0.0424296073076561</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60.27500152587891</v>
+        <v>61.11000061035156</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004968576784097678</v>
+        <v>0.01889056467783878</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.06236381166868743</v>
+        <v>-0.04937458995147304</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.73</v>
+        <v>-1.72</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>94811.33796691895</v>
+        <v>94188.23639831542</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.3%</t>
+          <t>+51.6%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-57235.51626586914</v>
+        <v>-57157.20050659179</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.7%</t>
+          <t>+33.4%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-37575.8217010498</v>
+        <v>-37031.03589172363</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46.27</v>
+        <v>45.71</v>
       </c>
       <c r="C2" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="D2" t="n">
-        <v>44.62</v>
+        <v>44.19</v>
       </c>
       <c r="E2" t="n">
-        <v>51.21</v>
+        <v>50.25</v>
       </c>
       <c r="F2" t="n">
-        <v>909.62</v>
+        <v>836.28</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.07</v>
+        <v>16.84</v>
       </c>
       <c r="C3" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="D3" t="n">
-        <v>16.35</v>
+        <v>16.16</v>
       </c>
       <c r="E3" t="n">
-        <v>19.24</v>
+        <v>18.87</v>
       </c>
       <c r="F3" t="n">
-        <v>1829.19</v>
+        <v>1711.82</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>244.85</v>
+        <v>245.75</v>
       </c>
       <c r="C5" t="n">
-        <v>9.640000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>235.21</v>
+        <v>236.45</v>
       </c>
       <c r="E5" t="n">
-        <v>273.78</v>
+        <v>273.66</v>
       </c>
       <c r="F5" t="n">
-        <v>1687.75</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>46.27000045776367</v>
+        <v>45.70999908447266</v>
       </c>
       <c r="F5" t="n">
-        <v>25541.04025268555</v>
+        <v>25231.91949462891</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>25541.04025268555</v>
+        <v>25231.91949462891</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>244.8500061035156</v>
+        <v>245.75</v>
       </c>
       <c r="F6" t="n">
-        <v>42848.75106811523</v>
+        <v>43006.25</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>42848.75106811523</v>
+        <v>43006.25</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.06999969482422</v>
+        <v>16.84000015258789</v>
       </c>
       <c r="F7" t="n">
-        <v>43152.95922851562</v>
+        <v>42571.52038574219</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>43152.95922851562</v>
+        <v>42571.52038574219</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4220.2998046875</v>
+        <v>4196.60009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01393460411830061</v>
+        <v>0.002268873391710224</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0424296073076561</v>
+        <v>-0.035685518548775</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61.11000061035156</v>
+        <v>60.36000061035156</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01889056467783878</v>
+        <v>-0.01320949952428541</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.04937458995147304</v>
+        <v>-0.04964337779178685</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.72</v>
+        <v>-1.7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>94188.23639831542</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.6%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-57157.20050659179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.4%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-37031.03589172363</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -717,20 +717,12 @@
           <t>PAAS</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>45.71</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44.19</v>
-      </c>
-      <c r="E2" t="n">
-        <v>50.25</v>
-      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>836.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -739,20 +731,12 @@
           <t>HL</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>16.84</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="D3" t="n">
-        <v>16.16</v>
-      </c>
-      <c r="E3" t="n">
-        <v>18.87</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>1711.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -775,20 +759,12 @@
           <t>FNV</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>245.75</v>
-      </c>
-      <c r="C5" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="D5" t="n">
-        <v>236.45</v>
-      </c>
-      <c r="E5" t="n">
-        <v>273.66</v>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>1628</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -980,20 +956,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>45.70999908447266</v>
-      </c>
-      <c r="F5" t="n">
-        <v>25231.91949462891</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Layer 2</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>25231.91949462891</v>
-      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1012,20 +982,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>245.75</v>
-      </c>
-      <c r="F6" t="n">
-        <v>43006.25</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Layer 2</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>43006.25</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1044,20 +1008,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>16.84000015258789</v>
-      </c>
-      <c r="F7" t="n">
-        <v>42571.52038574219</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Layer 3</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>42571.52038574219</v>
-      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1108,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4196.60009765625</v>
+        <v>4179</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002268873391710224</v>
+        <v>0.00924959617478649</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.035685518548775</v>
+        <v>-0.03549663303647432</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60.36000061035156</v>
+        <v>59.25</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.01320949952428541</v>
+        <v>-0.0108348766981976</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.04964337779178685</v>
+        <v>-0.06303371587684048</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.7</v>
+        <v>-1.52</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4179</v>
+        <v>4145.39990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00924959617478649</v>
+        <v>0.001135002972823429</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.03549663303647432</v>
+        <v>-0.04325145651571738</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59.25</v>
+        <v>55.95999908447266</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0108348766981976</v>
+        <v>-0.065760685327238</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.06303371587684048</v>
+        <v>-0.1150610565111603</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.52</v>
+        <v>-1.21</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4145.39990234375</v>
+        <v>4174.2998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001135002972823429</v>
+        <v>-0.009961340973264288</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04325145651571738</v>
+        <v>-0.05123085224423807</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55.95999908447266</v>
+        <v>57.24499893188477</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.065760685327238</v>
+        <v>-0.05645293127458306</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1150610565111603</v>
+        <v>-0.1256300921866704</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.21</v>
+        <v>-1.39</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4174.2998046875</v>
+        <v>4186.7001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.009961340973264288</v>
+        <v>-0.007020280991900107</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.05123085224423807</v>
+        <v>-0.04841238960484928</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57.24499893188477</v>
+        <v>57.1349983215332</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.05645293127458306</v>
+        <v>-0.05826602858250196</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1256300921866704</v>
+        <v>-0.12731026032934</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.39</v>
+        <v>-1.52</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4186.7001953125</v>
+        <v>4152.5</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.007020280991900107</v>
+        <v>-0.005936802682841025</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04841238960484928</v>
+        <v>-0.05278402963079454</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57.1349983215332</v>
+        <v>56.9900016784668</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.05826602858250196</v>
+        <v>-0.03669643253809585</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.12731026032934</v>
+        <v>-0.134219455820443</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.52</v>
+        <v>-1.45</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4152.5</v>
+        <v>4137.7998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.005936802682841025</v>
+        <v>0.007278634595426992</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.05278402963079454</v>
+        <v>-0.0545197200851022</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56.9900016784668</v>
+        <v>58.11000061035156</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.03669643253809585</v>
+        <v>0.04608463381549588</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.134219455820443</v>
+        <v>-0.1186373641073387</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.45</v>
+        <v>-1.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4137.7998046875</v>
+        <v>4135.7001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007278634595426992</v>
+        <v>-0.008249179045626276</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0545197200851022</v>
+        <v>-0.04230726916515826</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58.11000061035156</v>
+        <v>57.60499954223633</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04608463381549588</v>
+        <v>0.0135122845570641</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1186373641073387</v>
+        <v>-0.1052624001057986</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.5</v>
+        <v>-1.51</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4135.7001953125</v>
+        <v>4037.39990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.008249179045626276</v>
+        <v>-0.03436899188159892</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04230726916515826</v>
+        <v>-0.06063287521085392</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57.60499954223633</v>
+        <v>54.53499984741211</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0135122845570641</v>
+        <v>-0.04316166559477652</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1052624001057986</v>
+        <v>-0.140599158202119</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.51</v>
+        <v>-1.29</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4037.39990234375</v>
+        <v>4010</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.03436899188159892</v>
+        <v>-0.04092226774292285</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.06063287521085392</v>
+        <v>-0.06700791065611911</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54.53499984741211</v>
+        <v>53.95999908447266</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.04316166559477652</v>
+        <v>-0.05325028343345117</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.140599158202119</v>
+        <v>-0.1496604241980342</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.29</v>
+        <v>-1.16</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4010</v>
+        <v>4026.5</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.04092226774292285</v>
+        <v>-0.02802590038124508</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.06700791065611911</v>
+        <v>-0.03404181596491362</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53.95999908447266</v>
+        <v>54.13000106811523</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.05325028343345117</v>
+        <v>-0.06196929494670622</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1496604241980342</v>
+        <v>-0.1158118263837967</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.16</v>
+        <v>-1.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4026.5</v>
+        <v>4075.800048828125</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02802590038124508</v>
+        <v>-0.01787950630647595</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.03404181596491362</v>
+        <v>-0.02485827729962498</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54.13000106811523</v>
+        <v>54.43999862670898</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.06196929494670622</v>
+        <v>-0.05193135405142668</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1158118263837967</v>
+        <v>-0.1026570962625675</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.2</v>
+        <v>-1.33</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>87264.5369758606</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>+53.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-54679.98484039307</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>+31.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-32584.55213546753</v>
       </c>
     </row>
   </sheetData>
@@ -717,12 +717,20 @@
           <t>PAAS</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>41.95</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.31</v>
+      </c>
+      <c r="E2" t="n">
+        <v>46.88</v>
+      </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>907.65</v>
       </c>
     </row>
     <row r="3">
@@ -731,12 +739,20 @@
           <t>HL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>17.08</v>
+      </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1821.97</v>
       </c>
     </row>
     <row r="4">
@@ -759,12 +775,20 @@
           <t>FNV</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="D5" t="n">
+        <v>232.12</v>
+      </c>
+      <c r="E5" t="n">
+        <v>258.85</v>
+      </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1169.63</v>
       </c>
     </row>
     <row r="6">
@@ -956,14 +980,20 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>41.95000076293945</v>
+      </c>
+      <c r="F5" t="n">
+        <v>23156.40042114258</v>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Layer 2</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>23156.40042114258</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -982,14 +1012,20 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>238.8000030517578</v>
+      </c>
+      <c r="F6" t="n">
+        <v>41790.00053405762</v>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Layer 2</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>41790.00053405762</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1008,14 +1044,20 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>14.92000007629395</v>
+      </c>
+      <c r="F7" t="n">
+        <v>37717.76019287109</v>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Layer 3</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>37717.76019287109</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1066,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4075.800048828125</v>
+        <v>4078.10009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.01787950630647595</v>
+        <v>0.004359224642450421</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.02485827729962498</v>
+        <v>-0.02593930603816352</v>
       </c>
     </row>
     <row r="3">
@@ -1082,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54.43999862670898</v>
+        <v>54.24499893188477</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.05193135405142668</v>
+        <v>-0.009477047105005298</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1026570962625675</v>
+        <v>-0.09739093950678956</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.33</v>
+        <v>-1.18</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>87264.5369758606</v>
+        <v>84620.56049804688</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-54679.98484039307</v>
+        <v>-53068.64100952148</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-32584.55213546753</v>
+        <v>-31551.91948852539</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41.95</v>
+        <v>40.75</v>
       </c>
       <c r="C2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="D2" t="n">
-        <v>40.31</v>
+        <v>39.1</v>
       </c>
       <c r="E2" t="n">
-        <v>46.88</v>
+        <v>45.69</v>
       </c>
       <c r="F2" t="n">
-        <v>907.65</v>
+        <v>908.4299999999999</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.92</v>
+        <v>14.45</v>
       </c>
       <c r="C3" t="n">
         <v>0.72</v>
       </c>
       <c r="D3" t="n">
-        <v>14.2</v>
+        <v>13.73</v>
       </c>
       <c r="E3" t="n">
-        <v>17.08</v>
+        <v>16.6</v>
       </c>
       <c r="F3" t="n">
-        <v>1821.97</v>
+        <v>1811.13</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>238.8</v>
+        <v>231.6</v>
       </c>
       <c r="C5" t="n">
-        <v>6.68</v>
+        <v>6.82</v>
       </c>
       <c r="D5" t="n">
-        <v>232.12</v>
+        <v>224.78</v>
       </c>
       <c r="E5" t="n">
-        <v>258.85</v>
+        <v>252.07</v>
       </c>
       <c r="F5" t="n">
-        <v>1169.63</v>
+        <v>1194.25</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>41.95000076293945</v>
+        <v>40.75</v>
       </c>
       <c r="F5" t="n">
-        <v>23156.40042114258</v>
+        <v>22494</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>23156.40042114258</v>
+        <v>22494</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>238.8000030517578</v>
+        <v>231.6000061035156</v>
       </c>
       <c r="F6" t="n">
-        <v>41790.00053405762</v>
+        <v>40530.00106811523</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>41790.00053405762</v>
+        <v>40530.00106811523</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.92000007629395</v>
+        <v>14.44999980926514</v>
       </c>
       <c r="F7" t="n">
-        <v>37717.76019287109</v>
+        <v>36529.59951782227</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>37717.76019287109</v>
+        <v>36529.59951782227</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4078.10009765625</v>
+        <v>4013.10009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004359224642450421</v>
+        <v>0.00129748632431137</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.02593930603816352</v>
+        <v>-0.0450228959914295</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54.24499893188477</v>
+        <v>51.47000122070312</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.009477047105005298</v>
+        <v>-0.04172324804176364</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.09739093950678956</v>
+        <v>-0.1524083571177385</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.18</v>
+        <v>-1.25</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>84620.56049804688</v>
+        <v>80354.7912574768</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+53.3%</t>
+          <t>+53.8%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-53068.64100952148</v>
+        <v>-50877.70435943604</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+31.7%</t>
+          <t>+31.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-31551.91948852539</v>
+        <v>-29477.08689804077</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40.75</v>
+        <v>37.98</v>
       </c>
       <c r="C2" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="D2" t="n">
-        <v>39.1</v>
+        <v>36.15</v>
       </c>
       <c r="E2" t="n">
-        <v>45.69</v>
+        <v>43.47</v>
       </c>
       <c r="F2" t="n">
-        <v>908.4299999999999</v>
+        <v>1010.95</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.45</v>
+        <v>13.53</v>
       </c>
       <c r="C3" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="D3" t="n">
-        <v>13.73</v>
+        <v>12.75</v>
       </c>
       <c r="E3" t="n">
-        <v>16.6</v>
+        <v>15.87</v>
       </c>
       <c r="F3" t="n">
-        <v>1811.13</v>
+        <v>1971.84</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>231.6</v>
+        <v>224.95</v>
       </c>
       <c r="C5" t="n">
-        <v>6.82</v>
+        <v>7.33</v>
       </c>
       <c r="D5" t="n">
-        <v>224.78</v>
+        <v>217.62</v>
       </c>
       <c r="E5" t="n">
-        <v>252.07</v>
+        <v>246.93</v>
       </c>
       <c r="F5" t="n">
-        <v>1194.25</v>
+        <v>1282.38</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>40.75</v>
+        <v>37.97999954223633</v>
       </c>
       <c r="F5" t="n">
-        <v>22494</v>
+        <v>20964.95974731445</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>22494</v>
+        <v>20964.95974731445</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>231.6000061035156</v>
+        <v>224.9499969482422</v>
       </c>
       <c r="F6" t="n">
-        <v>40530.00106811523</v>
+        <v>39366.24946594238</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>40530.00106811523</v>
+        <v>39366.24946594238</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.44999980926514</v>
+        <v>13.52999973297119</v>
       </c>
       <c r="F7" t="n">
-        <v>36529.59951782227</v>
+        <v>34203.83932495117</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>36529.59951782227</v>
+        <v>34203.83932495117</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4013.10009765625</v>
+        <v>3884.89990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00129748632431137</v>
+        <v>-0.03068938920557163</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0450228959914295</v>
+        <v>-0.07553004713983114</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>51.47000122070312</v>
+        <v>49.1349983215332</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.04172324804176364</v>
+        <v>-0.08519670716283279</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1524083571177385</v>
+        <v>-0.1908604437022283</v>
       </c>
     </row>
   </sheetData>
